--- a/ig/DM-JUIN-2025/ValueSet-JDV-J107-EnsembleSavoirFaire-RASS.xlsx
+++ b/ig/DM-JUIN-2025/ValueSet-JDV-J107-EnsembleSavoirFaire-RASS.xlsx
@@ -17,12 +17,13 @@
     <sheet name="Include #7" r:id="rId11" sheetId="9"/>
     <sheet name="Include #8" r:id="rId12" sheetId="10"/>
     <sheet name="Include #9" r:id="rId13" sheetId="11"/>
+    <sheet name="Include #10" r:id="rId14" sheetId="12"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="570">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="573">
   <si>
     <t>Property</t>
   </si>
@@ -1732,6 +1733,15 @@
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/TRE_R359-SurspecialiteTransversale/FHIR/TRE-R359-SurspecialiteTransversale</t>
+  </si>
+  <si>
+    <t>CM0001</t>
+  </si>
+  <si>
+    <t>Certificat de décès</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r394-competence-metier</t>
   </si>
 </sst>
 </file>
@@ -2291,6 +2301,52 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>27</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>572</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:B106"/>
